--- a/output/pdf_financials_xlsx/KC.xlsx
+++ b/output/pdf_financials_xlsx/KC.xlsx
@@ -4603,37 +4603,37 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.216474</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.385794</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.431173</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.729834</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.417045</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.347984</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.886055</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.765888</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.929856</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.246758</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.747504</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -5702,16 +5702,16 @@
         <v>0.922735</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.462693</v>
+        <v>-0.311522</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>1.341646</v>
+        <v>0.8080540000000001</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.5706560000000001</v>
+        <v>0.5704669999999999</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.0106</v>
+        <v>-29.392082</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0.070116</v>
@@ -5729,10 +5729,10 @@
         <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.827304</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-1.827304</v>
       </c>
     </row>
     <row r="119">
@@ -8130,7 +8130,11 @@
           <t>Share‐based payment reserve 12 5,678,958</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -9748,7 +9752,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -11066,7 +11074,11 @@
           <t>Share‐based payment reserve 15, 16</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -13554,7 +13566,11 @@
           <t>Share-based payment reserve 16</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -15382,7 +15398,11 @@
           <t>Share-based payment reserve 15</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -16304,7 +16324,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -17066,7 +17090,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="n">
         <v>1.216474</v>
       </c>
@@ -18746,7 +18774,11 @@
           <t>Exploration and evaluation expenditures (356,926)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -20344,7 +20376,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -24634,7 +24670,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -26300,7 +26340,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KC.xlsx
+++ b/output/pdf_financials_xlsx/KC.xlsx
@@ -909,13 +909,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002284</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001732</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.013939</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.00042</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1618,13 +1618,13 @@
         <v>-1.570106</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.966572</v>
+        <v>-3.964288</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.053338</v>
+        <v>-5.05507</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.035172</v>
+        <v>-5.049111</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-3.735198</v>
@@ -1633,7 +1633,7 @@
         <v>-4.899362</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>15.797797</v>
+        <v>15.797377</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-1.10914</v>
@@ -1706,13 +1706,13 @@
         <v>-1.570106</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.964352</v>
+        <v>-3.962068</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.043864</v>
+        <v>-5.045596</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.023917</v>
+        <v>-5.037856</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-3.726163</v>
@@ -1721,7 +1721,7 @@
         <v>-4.897582</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>15.797797</v>
+        <v>15.797377</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-1.10914</v>
@@ -1937,25 +1937,25 @@
         <v>0.000406</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.216318</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.136892</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.265774</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.31422</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.903409</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.844984</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.901674</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2027,25 +2027,25 @@
         <v>0.424074</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.180341</v>
+        <v>4.396659</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.037568</v>
+        <v>0.17446</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.283274</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.209</v>
+        <v>3.52322</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.903409</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.844984</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.901674</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -2567,13 +2567,13 @@
         <v>0.004853</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.272632</v>
+        <v>1.056314</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.693734</v>
+        <v>1.556842</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.305236</v>
+        <v>0.039462</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -2582,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.110937</v>
+        <v>0.265953</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.985859</v>
+        <v>0.084185</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7120,7 +7120,11 @@
           <t>Reclamation deposit 6,10 182,900</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -8594,7 +8598,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -8870,7 +8874,11 @@
           <t>Reclamation deposit 6,10</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -10326,7 +10334,11 @@
           <t>Reclamation deposit 8,14</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -11770,7 +11782,11 @@
           <t>Reclamation deposit 8,14</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -12972,7 +12988,11 @@
           <t>Reclamation deposit 9</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -14708,7 +14728,11 @@
           <t>Reclamation deposit 8</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -24290,7 +24314,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -29824,7 +29852,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -32414,7 +32442,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -32492,7 +32520,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -38810,7 +38838,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -42464,7 +42492,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -44948,7 +44976,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E511" s="5" t="n">

--- a/output/pdf_financials_xlsx/KC.xlsx
+++ b/output/pdf_financials_xlsx/KC.xlsx
@@ -688,28 +688,28 @@
         <v>0.655072</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.188938</v>
+        <v>1.210175</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.406497</v>
+        <v>1.504232</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.992116</v>
+        <v>1.000264</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.974977</v>
+        <v>0.9878209999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.431911</v>
+        <v>1.509286</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.543824</v>
+        <v>1.662529</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.145112</v>
+        <v>1.242271</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.145112</v>
+        <v>1.242271</v>
       </c>
     </row>
     <row r="8">
@@ -1144,7 +1144,7 @@
         <v>-0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.972</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1317,15 +1317,11 @@
       <c r="J20" s="3" t="n">
         <v>-4.899362</v>
       </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K20" s="3" t="n">
+        <v>15.797797</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>-4.08114</v>
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
@@ -1456,7 +1452,7 @@
         <v>15.797797</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-1.10914</v>
+        <v>-4.08114</v>
       </c>
       <c r="M23" s="1" t="inlineStr">
         <is>
@@ -1591,7 +1587,7 @@
         <v>121.521515</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>36.971333</v>
+        <v>136.038</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -1836,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-267.9553527958598</v>
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
@@ -3472,10 +3468,8 @@
       <c r="L67" s="3" t="n">
         <v>0.045126</v>
       </c>
-      <c r="M67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M67" s="3" t="n">
+        <v>0.011477</v>
       </c>
     </row>
     <row r="68">
@@ -4910,7 +4904,7 @@
         <v>15.797797</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>-1.10914</v>
+        <v>-4.08114</v>
       </c>
       <c r="M99" s="1" t="inlineStr">
         <is>
@@ -5576,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -18174,7 +18168,11 @@
           <t>Deferred tax expense 681,000</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -19340,7 +19338,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -19784,7 +19786,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -26218,7 +26224,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -29164,7 +29174,11 @@
           <t>Directors’ fees 13 53,703</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -31814,7 +31828,11 @@
           <t>Directors’ fees 13</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -33732,7 +33750,11 @@
           <t>Directors’ fees 17</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -41046,7 +41068,11 @@
           <t>Directors’ fees 16</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
